--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754994</v>
+        <v>121754891</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525522</v>
+        <v>525579</v>
       </c>
       <c r="R3" t="n">
-        <v>6343574</v>
+        <v>6343544</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754891</v>
+        <v>121754994</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +896,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525579</v>
+        <v>525522</v>
       </c>
       <c r="R4" t="n">
-        <v>6343544</v>
+        <v>6343574</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754762</v>
+        <v>121754994</v>
       </c>
       <c r="B2" t="n">
         <v>57510</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525632</v>
+        <v>525522</v>
       </c>
       <c r="R2" t="n">
-        <v>6343363</v>
+        <v>6343574</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754994</v>
+        <v>121754762</v>
       </c>
       <c r="B4" t="n">
         <v>57510</v>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525522</v>
+        <v>525632</v>
       </c>
       <c r="R4" t="n">
-        <v>6343574</v>
+        <v>6343363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754994</v>
+        <v>121754891</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525522</v>
+        <v>525579</v>
       </c>
       <c r="R2" t="n">
-        <v>6343574</v>
+        <v>6343544</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754891</v>
+        <v>121754994</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525579</v>
+        <v>525522</v>
       </c>
       <c r="R3" t="n">
-        <v>6343544</v>
+        <v>6343574</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754891</v>
+        <v>121754762</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525579</v>
+        <v>525632</v>
       </c>
       <c r="R2" t="n">
-        <v>6343544</v>
+        <v>6343363</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754994</v>
+        <v>121754891</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525522</v>
+        <v>525579</v>
       </c>
       <c r="R3" t="n">
-        <v>6343574</v>
+        <v>6343544</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754762</v>
+        <v>121754994</v>
       </c>
       <c r="B4" t="n">
         <v>57510</v>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525632</v>
+        <v>525522</v>
       </c>
       <c r="R4" t="n">
-        <v>6343363</v>
+        <v>6343574</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754762</v>
+        <v>121754891</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525632</v>
+        <v>525579</v>
       </c>
       <c r="R2" t="n">
-        <v>6343363</v>
+        <v>6343544</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754891</v>
+        <v>121754762</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525579</v>
+        <v>525632</v>
       </c>
       <c r="R3" t="n">
-        <v>6343544</v>
+        <v>6343363</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754891</v>
+        <v>121754994</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>57518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525579</v>
+        <v>525522</v>
       </c>
       <c r="R2" t="n">
-        <v>6343544</v>
+        <v>6343574</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754762</v>
+        <v>121754891</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525632</v>
+        <v>525579</v>
       </c>
       <c r="R3" t="n">
-        <v>6343363</v>
+        <v>6343544</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754994</v>
+        <v>121754762</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525522</v>
+        <v>525632</v>
       </c>
       <c r="R4" t="n">
-        <v>6343574</v>
+        <v>6343363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754891</v>
+        <v>121754762</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +794,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525579</v>
+        <v>525632</v>
       </c>
       <c r="R3" t="n">
-        <v>6343544</v>
+        <v>6343363</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754762</v>
+        <v>121754891</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,46 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525632</v>
+        <v>525579</v>
       </c>
       <c r="R4" t="n">
-        <v>6343363</v>
+        <v>6343544</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754762</v>
+        <v>121754891</v>
       </c>
       <c r="B3" t="n">
-        <v>57518</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525632</v>
+        <v>525579</v>
       </c>
       <c r="R3" t="n">
-        <v>6343363</v>
+        <v>6343544</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754891</v>
+        <v>121754762</v>
       </c>
       <c r="B4" t="n">
-        <v>98133</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,41 +896,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östergård, Östergård, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525579</v>
+        <v>525632</v>
       </c>
       <c r="R4" t="n">
-        <v>6343544</v>
+        <v>6343363</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121754994</v>
       </c>
       <c r="B2" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121754891</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>121754762</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>121754994</v>
       </c>
       <c r="B4" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -902,11 +902,6 @@
       <c r="E4" t="n">
         <v>103021</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>121754994</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,6 +901,11 @@
       </c>
       <c r="E4" t="n">
         <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>121754994</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,6 +992,121 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128670544</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92782</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Börjes kulle, Rösjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>525545</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6343453</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Näshult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Slänt med äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martina Röed</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martina Röed</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128670544</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1107,6 +1107,140 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129505684</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Börjes kulle, Rösjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>525545</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6343453</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näshult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martina Röed</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martina Röed</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129505684</v>
       </c>
       <c r="B6" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129505684</v>
       </c>
       <c r="B6" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129505684</v>
+        <v>129667535</v>
       </c>
       <c r="B6" t="n">
         <v>91567</v>
@@ -1139,29 +1139,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Börjes kulle, Rösjön, Sm</t>
+          <t>Ålakistan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525545</v>
+        <v>525630</v>
       </c>
       <c r="R6" t="n">
-        <v>6343453</v>
+        <v>6343661</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>91601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>129667535</v>
       </c>
       <c r="B6" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91737</v>
+        <v>91738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -1246,7 +1246,7 @@
         <v>130447456</v>
       </c>
       <c r="B7" t="n">
-        <v>91739</v>
+        <v>91747</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>130447344</v>
       </c>
       <c r="B8" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 43195-2023 artfynd.xlsx
+++ b/artfynd/A 43195-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130447344</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130447456</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128670544</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121754762</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121754891</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505373</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129667535</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1606,8 +1646,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121754994</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>